--- a/data/b2_bonsucesso/B2 Bonsucesso 05-2026.xlsx
+++ b/data/b2_bonsucesso/B2 Bonsucesso 05-2026.xlsx
@@ -4810,61 +4810,61 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1752.09</v>
+        <v>1662.76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>1482.23</v>
+        <v>65122.77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>65787.97</v>
+        <v>1094.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>1497.55</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="6">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>3959.4</v>
+        <v>4062.19</v>
       </c>
     </row>
     <row r="8">
@@ -4914,11 +4914,11 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>999.76</v>
+        <v>1383.8</v>
       </c>
     </row>
     <row r="9">
@@ -4936,7 +4936,7 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1169.92</v>
+        <v>1441.82</v>
       </c>
     </row>
     <row r="10">
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>10599.7</v>
+        <v>9277.219999999999</v>
       </c>
     </row>
     <row r="11">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1996.65</v>
+        <v>2189.94</v>
       </c>
     </row>
     <row r="12">
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>4041.7</v>
+        <v>4022.18</v>
       </c>
     </row>
     <row r="13">
@@ -5008,25 +5008,25 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>22654.53</v>
+        <v>23092.63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46166</v>
+        <v>46163</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>2244.92</v>
+        <v>1287.76</v>
       </c>
     </row>
     <row r="15">
@@ -5035,34 +5035,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>4134.25</v>
+        <v>2063.85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46168</v>
+        <v>46166</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Limpeza da caixa separadora</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3294.98</v>
+        <v>3948.95</v>
       </c>
     </row>
     <row r="17">
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3933.79</v>
+        <v>3933.96</v>
       </c>
     </row>
   </sheetData>
